--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>127128027</v>
       </c>
       <c r="B3" t="n">
-        <v>92727</v>
+        <v>92802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128021</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128027</v>
+        <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>92802</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774917</v>
+        <v>774759</v>
       </c>
       <c r="R3" t="n">
-        <v>7128651</v>
+        <v>7128688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128021</v>
+        <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>92808</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774759</v>
+        <v>774917</v>
       </c>
       <c r="R4" t="n">
-        <v>7128688</v>
+        <v>7128651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128021</v>
+        <v>127128027</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>92808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774759</v>
+        <v>774917</v>
       </c>
       <c r="R3" t="n">
-        <v>7128688</v>
+        <v>7128651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128027</v>
+        <v>127128021</v>
       </c>
       <c r="B4" t="n">
-        <v>92808</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774917</v>
+        <v>774759</v>
       </c>
       <c r="R4" t="n">
-        <v>7128651</v>
+        <v>7128688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128027</v>
+        <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>92808</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774917</v>
+        <v>774759</v>
       </c>
       <c r="R3" t="n">
-        <v>7128651</v>
+        <v>7128688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128021</v>
+        <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>92809</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774759</v>
+        <v>774917</v>
       </c>
       <c r="R4" t="n">
-        <v>7128688</v>
+        <v>7128651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128025</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128021</v>
+        <v>127128027</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>92813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774759</v>
+        <v>774917</v>
       </c>
       <c r="R3" t="n">
-        <v>7128688</v>
+        <v>7128651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128027</v>
+        <v>127128021</v>
       </c>
       <c r="B4" t="n">
-        <v>92809</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774917</v>
+        <v>774759</v>
       </c>
       <c r="R4" t="n">
-        <v>7128651</v>
+        <v>7128688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
         <v>127128026</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128025</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127128027</v>
       </c>
       <c r="B3" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128021</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>127128026</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>127128027</v>
       </c>
       <c r="B3" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128025</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128027</v>
+        <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>92821</v>
+        <v>79641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>774917</v>
+        <v>774759</v>
       </c>
       <c r="R3" t="n">
-        <v>7128651</v>
+        <v>7128688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127128021</v>
+        <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>92824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774759</v>
+        <v>774917</v>
       </c>
       <c r="R4" t="n">
-        <v>7128688</v>
+        <v>7128651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
         <v>127128026</v>
       </c>
       <c r="B5" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128025</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>127128026</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128025</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,14 +776,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>79739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,14 +877,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>92989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,14 +978,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127128026</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,14 +1087,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91314</v>
+        <v>91469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,14 +1188,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>79739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,14 +1289,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1390,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128025</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127128026</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128025</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127128026</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128025</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127128026</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128025</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127128026</v>
       </c>
       <c r="B5" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>127128021</v>
       </c>
       <c r="B3" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127128020</v>
       </c>
       <c r="B7" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127128028</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32829-2025 artfynd.xlsx
+++ b/artfynd/A 32829-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>127128027</v>
       </c>
       <c r="B4" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127128019</v>
       </c>
       <c r="B6" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
